--- a/tame_output/ON/bt/strategyON_20240403.xlsx
+++ b/tame_output/ON/bt/strategyON_20240403.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-478.3%</t>
+          <t>-478.4%</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-193.6%</t>
+          <t>-193.7%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-14.9%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-210.7%</t>
+          <t>-210.9%</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-128.7%</t>
+          <t>-128.8%</t>
         </is>
       </c>
     </row>
@@ -45757,16 +45757,16 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-3.167081831777972</v>
+        <v>-3.168509623619477</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.825925766606518</v>
+        <v>1.825354649869916</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.1327772684100859</v>
+        <v>0.1313494765685818</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.172781284677507</v>
+        <v>3.171924609572604</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240403.xlsx
+++ b/tame_output/ON/bt/strategyON_20240403.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>44.6%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.8%</t>
+          <t>111.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>129.1%</t>
+          <t>129.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-604.1%</t>
+          <t>-602.9%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-68.7%</t>
+          <t>-68.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.5%</t>
+          <t>92.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>495.3%</t>
+          <t>499.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-478.4%</t>
+          <t>-477.9%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-242.0%</t>
+          <t>-241.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-159.3%</t>
+          <t>-152.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-193.7%</t>
+          <t>-193.5%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-23.2%</t>
+          <t>-23.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.1%</t>
+          <t>70.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-306.6%</t>
+          <t>-305.4%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,22 +1313,22 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.8%</t>
+          <t>-33.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-161.1%</t>
+          <t>-160.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-210.9%</t>
+          <t>-210.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.8%</t>
+          <t>96.7%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-184.4%</t>
+          <t>-183.6%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,22 +1471,22 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.1%</t>
+          <t>-29.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1496,12 +1496,12 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-128.8%</t>
+          <t>-128.5%</t>
         </is>
       </c>
     </row>
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130021</v>
+        <v>3.287377576130022</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.660017067431099</v>
+        <v>-3.648244874482496</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.671602468576933</v>
+        <v>1.676311345756374</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.6071902478558189</v>
+        <v>-0.5954180549072157</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.771651571149629</v>
+        <v>2.778714886918791</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.666678007653247</v>
+        <v>-3.654905814704644</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.670711019188333</v>
+        <v>1.675419896367774</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.6071902478558189</v>
+        <v>-0.5954180549072157</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.773424497849888</v>
+        <v>2.78048781361905</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207817</v>
+        <v>3.305316798207818</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.098483800803034</v>
+        <v>-4.086711607854431</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.484321589395822</v>
+        <v>1.489030466575264</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.7436077442970859</v>
+        <v>-0.7318355513484827</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.677906887452532</v>
+        <v>2.684970203221694</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310986</v>
+        <v>3.284619513310987</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.424916329670778</v>
+        <v>-4.413144136722175</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.342033352850815</v>
+        <v>1.346742230030257</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.826075994804234</v>
+        <v>-0.8143038018556308</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.616710712150335</v>
+        <v>2.623774027919496</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006537</v>
+        <v>3.305849539006538</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.426480480781081</v>
+        <v>-4.414708287832478</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.33998828406266</v>
+        <v>1.344697161242101</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.826075994804234</v>
+        <v>-0.8143038018556308</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.6152913038063</v>
+        <v>2.622354619575462</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309428</v>
+        <v>3.311086391309429</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.790106725681395</v>
+        <v>-4.778334532732791</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.201025346336776</v>
+        <v>1.205734223516217</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9242976316713598</v>
+        <v>-0.9125254387227566</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.562845881920266</v>
+        <v>2.569909197689427</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970909</v>
+        <v>3.30471571697091</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.787679661152676</v>
+        <v>-4.775907468204073</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.201250687154094</v>
+        <v>1.205959564333536</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.9246304134785115</v>
+        <v>-0.9128582205299083</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.561900727841806</v>
+        <v>2.568964043610968</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330526</v>
+        <v>3.300815818330527</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.196268438333354</v>
+        <v>-5.184496245384751</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.036576720296582</v>
+        <v>1.041285597476024</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.33321919065919</v>
+        <v>-1.321446997710587</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.315509005548158</v>
+        <v>2.32257232131732</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191741</v>
+        <v>3.302618194191742</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.609250922474448</v>
+        <v>-5.597478729525845</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.8665691591116054</v>
+        <v>0.8712780362910468</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.33321919065919</v>
+        <v>-1.321446997710587</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.310694438019619</v>
+        <v>2.317757753788781</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.025642796761446</v>
+        <v>-6.013870603812842</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.6980064600056837</v>
+        <v>0.7027153371851251</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.33321919065919</v>
+        <v>-1.321446997710587</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.308688488628496</v>
+        <v>2.315751804397658</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097825</v>
+        <v>3.341378723097826</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.40231980729129</v>
+        <v>-6.390547614342687</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.5575943464624249</v>
+        <v>0.5623032236418664</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.33321919065919</v>
+        <v>-1.321446997710587</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.318947179297175</v>
+        <v>2.326010495066337</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094121</v>
+        <v>3.374439043094122</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.416034671616401</v>
+        <v>-6.404262478667798</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.5482079658780754</v>
+        <v>0.5529168430575169</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.33321919065919</v>
+        <v>-1.321446997710587</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.31504674444287</v>
+        <v>2.322110060212032</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119929</v>
+        <v>3.405960511199291</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.728859470861381</v>
+        <v>-6.717087277912777</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.4214829662350845</v>
+        <v>0.426191843414526</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.33321919065919</v>
+        <v>-1.321446997710587</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.313451664497871</v>
+        <v>2.320514980267033</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969599</v>
+        <v>3.4246333549696</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.733672509326718</v>
+        <v>-6.721900316378115</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.423336726778158</v>
+        <v>0.4280456039575995</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.334765825361976</v>
+        <v>-1.322993632413373</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.316302659605408</v>
+        <v>2.323365975374569</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923092</v>
+        <v>3.419979433923093</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.167021617436954</v>
+        <v>-7.155249424488351</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.2459707789996606</v>
+        <v>0.250679656179102</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.334765825361976</v>
+        <v>-1.322993632413373</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.312276355071005</v>
+        <v>2.319339670840167</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297754</v>
+        <v>3.458100091297755</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.550023006179585</v>
+        <v>-7.538250813230982</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.09266812218102416</v>
+        <v>0.09737699936046518</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.334765825361976</v>
+        <v>-1.322993632413373</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.312174253749421</v>
+        <v>2.319237569518583</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317621</v>
+        <v>3.447750501317622</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.925008332350862</v>
+        <v>-7.913236139402259</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.05475449231605678</v>
+        <v>-0.05004561513661532</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.709751151533253</v>
+        <v>-1.69797895858465</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.089754574018084</v>
+        <v>2.096817889787246</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737175</v>
+        <v>3.503515506737176</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.284538654854863</v>
+        <v>-8.272766461906262</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.1932163180196071</v>
+        <v>-0.1885074408401657</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.709751151533253</v>
+        <v>-1.69797895858465</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.095104877316134</v>
+        <v>2.102168193085296</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341318</v>
+        <v>3.503170282341319</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.610938683519876</v>
+        <v>-8.599166490571275</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.3158603095284351</v>
+        <v>-0.3111514323489937</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.036151180198266</v>
+        <v>-2.024378987249663</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.907180880074304</v>
+        <v>1.914244195843466</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.604462536726317</v>
+        <v>-8.592690343777715</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.3102281001892422</v>
+        <v>-0.3055192230098007</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.029675033404706</v>
+        <v>-2.017902840456103</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.914108318772209</v>
+        <v>1.921171634541371</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.600771611769906</v>
+        <v>-8.588999418821304</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.3087517302066778</v>
+        <v>-0.3040428530272368</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.029675033404706</v>
+        <v>-2.017902840456103</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.914108318772209</v>
+        <v>1.921171634541371</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.80502978709977</v>
+        <v>-8.793257594151168</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3849418032199812</v>
+        <v>-0.3802329260405397</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.157313978018695</v>
+        <v>-2.145541785070092</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.843038149122458</v>
+        <v>1.85010146489162</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.965668813588135</v>
+        <v>-8.953896620639533</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.4447148593308912</v>
+        <v>-0.4400059821514497</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.272047451021091</v>
+        <v>-2.260275258072488</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.778680619805457</v>
+        <v>1.785743935574619</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.892198981920686</v>
+        <v>-8.880426788972084</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.3999552251704905</v>
+        <v>-0.3952463479910491</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.198577619353642</v>
+        <v>-2.186805426405039</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.838134220299347</v>
+        <v>1.845197536068509</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.067323399307229</v>
+        <v>-9.055551206358627</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.4554497713775909</v>
+        <v>-0.4507408941981494</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.373702036740186</v>
+        <v>-2.361929843791583</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.747614790614937</v>
+        <v>1.754678106384099</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587501888027</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.301775493321719</v>
+        <v>-9.290003300373117</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.556449773884983</v>
+        <v>-0.5517408967055415</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.373702036740186</v>
+        <v>-2.361929843791583</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.740395625713341</v>
+        <v>1.747458941482503</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234395</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.589579337858957</v>
+        <v>-9.577807144910356</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.6782435024738542</v>
+        <v>-0.6735346252944132</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.661505881277424</v>
+        <v>-2.649733688328821</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.561041128217022</v>
+        <v>1.568104443986184</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.819403785022782</v>
+        <v>-9.807631592074181</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.7690574915008281</v>
+        <v>-0.7643486143213867</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.824153418347585</v>
+        <v>-2.812381225398982</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.464568395813482</v>
+        <v>1.471631711582644</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767398</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.05143270475904</v>
+        <v>-10.03966051181044</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.859175330766218</v>
+        <v>-0.854466453586777</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.886166115536008</v>
+        <v>-2.874393922587405</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.430054506129543</v>
+        <v>1.437117821898705</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.999417190790231</v>
+        <v>-9.987644997841629</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.8343787894922921</v>
+        <v>-0.8296699123128506</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.886166115536008</v>
+        <v>-2.874393922587405</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.434044841815944</v>
+        <v>1.441108157585106</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.14108903251435</v>
+        <v>-10.12931683956575</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.8925227530806819</v>
+        <v>-0.8878138759012408</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.886166115536008</v>
+        <v>-2.874393922587405</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.432569614917202</v>
+        <v>1.439632930686364</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.23999577297363</v>
+        <v>-10.22822358002503</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.9170320390995195</v>
+        <v>-0.9123231619200785</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.985072855995284</v>
+        <v>-2.97330066304668</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.388278980806509</v>
+        <v>1.395342296575671</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240578</v>
+        <v>3.676837974240579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.04084366573653</v>
+        <v>-10.02907147278793</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.8504223298513636</v>
+        <v>-0.8457134526719217</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.81975033004547</v>
+        <v>-2.807978137096867</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.474421362729714</v>
+        <v>1.481484678498876</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.814998513017118</v>
+        <v>-9.803226320068514</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.7505051957273907</v>
+        <v>-0.7457963185479484</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.777823654458307</v>
+        <v>-2.766051461509703</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.509156441118221</v>
+        <v>1.516219756887383</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282102</v>
+        <v>3.684840248282103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.528723700694423</v>
+        <v>-9.516951507745819</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.6348561262422536</v>
+        <v>-0.6301472490628117</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.777823654458307</v>
+        <v>-2.766051461509703</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.51029558567428</v>
+        <v>1.517358901443442</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116217</v>
+        <v>3.710931958116218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.581618988738709</v>
+        <v>-9.569846795790106</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.6533804672978607</v>
+        <v>-0.6486715901184184</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.772868308369861</v>
+        <v>-2.761096115421257</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.515902567489455</v>
+        <v>1.522965883258617</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081569</v>
+        <v>3.76894809908157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.29771025780996</v>
+        <v>-9.285938064861357</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.5340832706877245</v>
+        <v>-0.5293743935082826</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.772868308369861</v>
+        <v>-2.761096115421257</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.521636271728092</v>
+        <v>1.528699587497254</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425329</v>
+        <v>3.728574354425331</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.050723007617009</v>
+        <v>-9.038950814668405</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.4450256330044091</v>
+        <v>-0.4403167558249672</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.525881058176909</v>
+        <v>-2.514108865228305</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.660091359449998</v>
+        <v>1.66715467521916</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702414</v>
+        <v>3.747699084702416</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.786886140412939</v>
+        <v>-8.775113947464336</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.3493743674356886</v>
+        <v>-0.3446654902562467</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.525881058176909</v>
+        <v>-2.514108865228305</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.65020787813709</v>
+        <v>1.657271193906252</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906229</v>
+        <v>3.766313503906231</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.519644339544541</v>
+        <v>-8.507872146595938</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2443122075877033</v>
+        <v>-0.2396033304082614</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.525881058176909</v>
+        <v>-2.514108865228305</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.648373317637716</v>
+        <v>1.655436633406878</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781949</v>
+        <v>3.784680945781951</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.243835176144056</v>
+        <v>-8.232062983195453</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1342888572009704</v>
+        <v>-0.129579980021528</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.436861749898175</v>
+        <v>-2.425089556949572</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.701484587631496</v>
+        <v>1.708547903400658</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567245</v>
+        <v>3.800825778567246</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-7.974767588377077</v>
+        <v>-7.962995395428473</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.0259933159486847</v>
+        <v>-0.0212844387692428</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.167794162131196</v>
+        <v>-2.156021969182592</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.863593646437177</v>
+        <v>1.870656962206339</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487774</v>
+        <v>3.789307536487775</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-7.710707650054281</v>
+        <v>-7.698935457105677</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.06637034321868152</v>
+        <v>0.07107922039812342</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.9037342238084</v>
+        <v>-1.891962030859796</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.008769293269102</v>
+        <v>2.015832609038264</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309728</v>
+        <v>3.833249172309729</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.003628026549443</v>
+        <v>-6.991855833600839</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.3464151589603159</v>
+        <v>0.3511240361397578</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.9037342238084</v>
+        <v>-1.891962030859796</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.005982259608801</v>
+        <v>2.013045575377963</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937087185873</v>
+        <v>3.839370871858731</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-6.753986996563491</v>
+        <v>-6.742214803614887</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.4466151948425381</v>
+        <v>0.45132407202198</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.654093193822448</v>
+        <v>-1.642321000873844</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.156110501488214</v>
+        <v>2.163173817257376</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096476</v>
+        <v>3.856158176096477</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-6.499445097222415</v>
+        <v>-6.487672904273811</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.5477987757997251</v>
+        <v>0.5525076529791675</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.399551294481372</v>
+        <v>-1.387779101532769</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.308202462313616</v>
+        <v>2.315265778082778</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761807</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.265963874992816</v>
+        <v>-6.254191682044213</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.6491156935294171</v>
+        <v>0.653824570708859</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.166070072251774</v>
+        <v>-1.15429787930317</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.456215624489228</v>
+        <v>2.46327894025839</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255784</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.086255344848944</v>
+        <v>-6.07448315190034</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.7181068952740071</v>
+        <v>0.722815772453449</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.108898568089078</v>
+        <v>-1.097126375140474</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.487626316673886</v>
+        <v>2.494689632443048</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860425</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-5.953979871218057</v>
+        <v>-5.942207678269454</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.7663845714733886</v>
+        <v>0.7710934486528309</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.9766230944581911</v>
+        <v>-0.9648509015095876</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.562359087599445</v>
+        <v>2.569422403368607</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-5.763380196544905</v>
+        <v>-5.751608003596301</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.8454395020302865</v>
+        <v>0.8501483792097284</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.7860234197850382</v>
+        <v>-0.7742512268364348</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.679533953090973</v>
+        <v>2.686597268860136</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430986</v>
+        <v>3.753878996430988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-5.514380397861324</v>
+        <v>-5.50260820491272</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.9579457627273777</v>
+        <v>0.9626546399068197</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.7860234197850382</v>
+        <v>-0.7742512268364348</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.692440294314632</v>
+        <v>2.699503610083794</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077644</v>
+        <v>3.692928280077645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-5.619970387634428</v>
+        <v>-5.608198194685825</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.7877338372189171</v>
+        <v>0.792442714398359</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.8916134095581425</v>
+        <v>-0.8798412166095391</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.501110370851551</v>
+        <v>2.508173686620713</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-5.638705289753025</v>
+        <v>-5.626933096804422</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.8287842182485647</v>
+        <v>0.8334930954280066</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.8916134095581425</v>
+        <v>-0.8798412166095391</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.549654712728637</v>
+        <v>2.5567180284978</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-5.361967115082212</v>
+        <v>-5.350194922133609</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.9428585001028846</v>
+        <v>0.9475673772823265</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.7097967484482167</v>
+        <v>-0.6980245554996133</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.662123721380588</v>
+        <v>2.669187037149749</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-5.235074708647142</v>
+        <v>-5.223302515698538</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.9849014764234343</v>
+        <v>0.9896103536028766</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.5829043420131468</v>
+        <v>-0.5711321490645433</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.729545178988151</v>
+        <v>2.736608494757313</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568105</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-5.047487200737216</v>
+        <v>-5.035715007788612</v>
       </c>
       <c r="E1912" t="n">
-        <v>1.052975867492312</v>
+        <v>1.057684744671754</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.5829043420131468</v>
+        <v>-0.5711321490645433</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.722584566893058</v>
+        <v>2.72964788266222</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963418</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-4.805338807283357</v>
+        <v>-4.793566614334754</v>
       </c>
       <c r="E1913" t="n">
-        <v>1.164297579254998</v>
+        <v>1.16900645643444</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.5829043420131468</v>
+        <v>-0.5711321490645433</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.737046921274201</v>
+        <v>2.744110237043363</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192815</v>
+        <v>3.828547911192817</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-4.742109435515009</v>
+        <v>-4.730337242566406</v>
       </c>
       <c r="E1914" t="n">
-        <v>1.184121448421533</v>
+        <v>1.188830325600974</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.5829043420131468</v>
+        <v>-0.5711321490645433</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.731579041733396</v>
+        <v>2.738642357502558</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262045</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-4.555621743138003</v>
+        <v>-4.5438495501894</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.256214619382912</v>
+        <v>1.260923496562354</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.3964166496361405</v>
+        <v>-0.3846444566875371</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.840969751170177</v>
+        <v>2.848033066939339</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389907</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-4.53447254423456</v>
+        <v>-4.522700351285956</v>
       </c>
       <c r="E1916" t="n">
-        <v>1.272375277181615</v>
+        <v>1.277084154361057</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.3752674507326972</v>
+        <v>-0.3634952577840938</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.861360248749568</v>
+        <v>2.86842356451873</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788093</v>
+        <v>3.748324832788095</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-4.290707102251115</v>
+        <v>-4.278934909302512</v>
       </c>
       <c r="E1917" t="n">
-        <v>1.365662162322043</v>
+        <v>1.370371039501485</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.3752674507326972</v>
+        <v>-0.3634952577840938</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.857140957096619</v>
+        <v>2.864204272865781</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527524</v>
+        <v>3.824307657527526</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-4.026679035057855</v>
+        <v>-4.014906842109252</v>
       </c>
       <c r="E1918" t="n">
-        <v>1.473397703119363</v>
+        <v>1.478106580298805</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.1734020519167436</v>
+        <v>-0.1616298589681402</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.980384510306207</v>
+        <v>2.987447826075369</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749183</v>
+        <v>3.826351398749185</v>
       </c>
       <c r="C1919" t="n">
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-3.77682864110878</v>
+        <v>-3.765056448160177</v>
       </c>
       <c r="E1919" t="n">
-        <v>1.566079935682695</v>
+        <v>1.570788812862137</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.1734020519167436</v>
+        <v>-0.1616298589681402</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.97312658528991</v>
+        <v>2.980189901059072</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481496</v>
+        <v>3.835954411481498</v>
       </c>
       <c r="C1920" t="n">
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-3.473261152104802</v>
+        <v>-3.461488959156199</v>
       </c>
       <c r="E1920" t="n">
-        <v>1.691106054804935</v>
+        <v>1.695814931984377</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.1734020519167436</v>
+        <v>-0.1616298589681402</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.976725708810558</v>
+        <v>2.98378902457972</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862985</v>
+        <v>3.780930335862987</v>
       </c>
       <c r="C1921" t="n">
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-3.399781243252788</v>
+        <v>-3.388009050304184</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.733825524400295</v>
+        <v>1.738534401579737</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.09992214306472924</v>
+        <v>-0.08814995011612581</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.034141160176321</v>
+        <v>3.041204475945483</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.41238645459175</v>
+        <v>3.727110450779685</v>
       </c>
       <c r="C1922" t="n">
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-3.168509623619477</v>
+        <v>-3.162976050635361</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.825354649869916</v>
+        <v>1.827568079063563</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.1313494765685818</v>
+        <v>0.136883049552697</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.171924609572604</v>
+        <v>3.175244753363073</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240403.xlsx
+++ b/tame_output/ON/bt/strategyON_20240403.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-04-02</t>
+          <t>2024-04-03</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>73.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-04-02</t>
+          <t>2024-04-03</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>1.5%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-74.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.7%</t>
+          <t>111.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-04-02</t>
+          <t>2024-04-03</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>129.0%</t>
+          <t>128.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.2%</t>
+          <t>92.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,11 +973,11 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-602.9%</t>
+          <t>-603.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-68.6%</t>
+          <t>-69.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.6%</t>
+          <t>92.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>499.6%</t>
+          <t>498.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-477.9%</t>
+          <t>-500.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-04-02</t>
+          <t>2024-04-03</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,11 +1131,11 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-241.5%</t>
+          <t>-241.6%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,12 +1180,12 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-152.5%</t>
+          <t>-152.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-193.5%</t>
+          <t>-202.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-23.0%</t>
+          <t>-25.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-04-02</t>
+          <t>2024-04-03</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,11 +1289,11 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-305.4%</t>
+          <t>-305.5%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-19.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-210.3%</t>
+          <t>-232.8%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-04-02</t>
+          <t>2024-04-03</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,11 +1447,11 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-183.6%</t>
+          <t>-183.7%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-128.5%</t>
+          <t>-133.6%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1922"/>
+  <dimension ref="A1:G1923"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130022</v>
+        <v>3.287377576130021</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.648244874482496</v>
+        <v>-3.649031488298536</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.676311345756374</v>
+        <v>1.675996700229958</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.5954180549072157</v>
+        <v>-0.5962046687232554</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.778714886918791</v>
+        <v>2.778242918629167</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.654905814704644</v>
+        <v>-3.655692428520684</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.675419896367774</v>
+        <v>1.675105250841359</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.5954180549072157</v>
+        <v>-0.5962046687232554</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.78048781361905</v>
+        <v>2.780015845329427</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.086711607854431</v>
+        <v>-4.08749822167047</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.489030466575264</v>
+        <v>1.488715821048848</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.7318355513484827</v>
+        <v>-0.7326221651645224</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.684970203221694</v>
+        <v>2.684498234932071</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310987</v>
+        <v>3.284619513310986</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.413144136722175</v>
+        <v>-4.413930750538214</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.346742230030257</v>
+        <v>1.346427584503841</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.8143038018556308</v>
+        <v>-0.8150904156716705</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.623774027919496</v>
+        <v>2.623302059629872</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.414708287832478</v>
+        <v>-4.415494901648517</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.344697161242101</v>
+        <v>1.344382515715685</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.8143038018556308</v>
+        <v>-0.8150904156716705</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.622354619575462</v>
+        <v>2.621882651285838</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309429</v>
+        <v>3.311086391309428</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.778334532732791</v>
+        <v>-4.779121146548831</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.205734223516217</v>
+        <v>1.205419577989801</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9125254387227566</v>
+        <v>-0.9133120525387963</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.569909197689427</v>
+        <v>2.569437229399804</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.30471571697091</v>
+        <v>3.304715716970909</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.775907468204073</v>
+        <v>-4.776694082020112</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.205959564333536</v>
+        <v>1.20564491880712</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.9128582205299083</v>
+        <v>-0.913644834345948</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.568964043610968</v>
+        <v>2.568492075321344</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330527</v>
+        <v>3.300815818330526</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.184496245384751</v>
+        <v>-5.18528285920079</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.041285597476024</v>
+        <v>1.040970951949608</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.321446997710587</v>
+        <v>-1.322233611526626</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.32257232131732</v>
+        <v>2.322100353027696</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191742</v>
+        <v>3.302618194191741</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.597478729525845</v>
+        <v>-5.598265343341884</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.8712780362910468</v>
+        <v>0.870963390764631</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.321446997710587</v>
+        <v>-1.322233611526626</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.317757753788781</v>
+        <v>2.317285785499157</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108644</v>
+        <v>3.305023265108643</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.013870603812842</v>
+        <v>-6.014657217628882</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.7027153371851251</v>
+        <v>0.7024006916587093</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.321446997710587</v>
+        <v>-1.322233611526626</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.315751804397658</v>
+        <v>2.315279836108034</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097826</v>
+        <v>3.341378723097825</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.390547614342687</v>
+        <v>-6.391334228158726</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.5623032236418664</v>
+        <v>0.5619885781154506</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.321446997710587</v>
+        <v>-1.322233611526626</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.326010495066337</v>
+        <v>2.325538526776713</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094122</v>
+        <v>3.374439043094121</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.404262478667798</v>
+        <v>-6.405049092483837</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.5529168430575169</v>
+        <v>0.5526021975311011</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.321446997710587</v>
+        <v>-1.322233611526626</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.322110060212032</v>
+        <v>2.321638091922408</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199291</v>
+        <v>3.40596051119929</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.717087277912777</v>
+        <v>-6.717873891728817</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.426191843414526</v>
+        <v>0.4258771978881102</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.321446997710587</v>
+        <v>-1.322233611526626</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.320514980267033</v>
+        <v>2.320043011977409</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.4246333549696</v>
+        <v>3.424633354969599</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.721900316378115</v>
+        <v>-6.722686930194154</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.4280456039575995</v>
+        <v>0.4277309584311837</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.322993632413373</v>
+        <v>-1.323780246229412</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.323365975374569</v>
+        <v>2.322894007084946</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923093</v>
+        <v>3.419979433923092</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.155249424488351</v>
+        <v>-7.15603603830439</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.250679656179102</v>
+        <v>0.2503650106526862</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.322993632413373</v>
+        <v>-1.323780246229412</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.319339670840167</v>
+        <v>2.318867702550543</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297755</v>
+        <v>3.458100091297754</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.538250813230982</v>
+        <v>-7.539037427047021</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.09737699936046518</v>
+        <v>0.09706235383404938</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.322993632413373</v>
+        <v>-1.323780246229412</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.319237569518583</v>
+        <v>2.318765601228959</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317622</v>
+        <v>3.447750501317621</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.913236139402259</v>
+        <v>-7.914022753218299</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.05004561513661532</v>
+        <v>-0.05036026066303112</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.69797895858465</v>
+        <v>-1.69876557240069</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.096817889787246</v>
+        <v>2.096345921497623</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737176</v>
+        <v>3.503515506737175</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.272766461906262</v>
+        <v>-8.273553075722301</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.1885074408401657</v>
+        <v>-0.1888220863665815</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.69797895858465</v>
+        <v>-1.69876557240069</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.102168193085296</v>
+        <v>2.101696224795673</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341319</v>
+        <v>3.503170282341318</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.599166490571275</v>
+        <v>-8.599953104387314</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.3111514323489937</v>
+        <v>-0.3114660778754095</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.024378987249663</v>
+        <v>-2.025165601065702</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.914244195843466</v>
+        <v>1.913772227553842</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.592690343777715</v>
+        <v>-8.593476957593754</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.3055192230098007</v>
+        <v>-0.3058338685362165</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.017902840456103</v>
+        <v>-2.018689454272143</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.921171634541371</v>
+        <v>1.920699666251747</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.588999418821304</v>
+        <v>-8.589786032637344</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.3040428530272368</v>
+        <v>-0.3043574985536526</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.017902840456103</v>
+        <v>-2.018689454272143</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.921171634541371</v>
+        <v>1.920699666251747</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.793257594151168</v>
+        <v>-8.794044207967207</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3802329260405397</v>
+        <v>-0.3805475715669555</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.145541785070092</v>
+        <v>-2.146328398886132</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.85010146489162</v>
+        <v>1.849629496601996</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.953896620639533</v>
+        <v>-8.954683234455572</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.4400059821514497</v>
+        <v>-0.4403206276778655</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.260275258072488</v>
+        <v>-2.261061871888527</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.785743935574619</v>
+        <v>1.785271967284995</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.880426788972084</v>
+        <v>-8.881213402788124</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.3952463479910491</v>
+        <v>-0.3955609935174649</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.186805426405039</v>
+        <v>-2.187592040221079</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.845197536068509</v>
+        <v>1.844725567778885</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.055551206358627</v>
+        <v>-9.056337820174667</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.4507408941981494</v>
+        <v>-0.4510555397245652</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.361929843791583</v>
+        <v>-2.362716457607623</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.754678106384099</v>
+        <v>1.754206138094476</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.48587501888027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.290003300373117</v>
+        <v>-9.290789914189157</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.5517408967055415</v>
+        <v>-0.5520555422319573</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.361929843791583</v>
+        <v>-2.362716457607623</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.747458941482503</v>
+        <v>1.74698697319288</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.577807144910356</v>
+        <v>-9.578593758726395</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.6735346252944132</v>
+        <v>-0.673849270820829</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.649733688328821</v>
+        <v>-2.650520302144861</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.568104443986184</v>
+        <v>1.56763247569656</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.807631592074181</v>
+        <v>-9.80841820589022</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.7643486143213867</v>
+        <v>-0.7646632598478025</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.812381225398982</v>
+        <v>-2.813167839215021</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.471631711582644</v>
+        <v>1.47115974329302</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.492098065767398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.03966051181044</v>
+        <v>-10.04044712562648</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.854466453586777</v>
+        <v>-0.8547810991131928</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.874393922587405</v>
+        <v>-2.875180536403445</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.437117821898705</v>
+        <v>1.436645853609081</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792544</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.987644997841629</v>
+        <v>-9.988431611657669</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.8296699123128506</v>
+        <v>-0.8299845578392664</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.874393922587405</v>
+        <v>-2.875180536403445</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.441108157585106</v>
+        <v>1.440636189295482</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.12931683956575</v>
+        <v>-10.13010345338179</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.8878138759012408</v>
+        <v>-0.8881285214276566</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.874393922587405</v>
+        <v>-2.875180536403445</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.439632930686364</v>
+        <v>1.43916096239674</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410719</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.22822358002503</v>
+        <v>-10.22901019384106</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.9123231619200785</v>
+        <v>-0.9126378074464943</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.97330066304668</v>
+        <v>-2.97408727686272</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.395342296575671</v>
+        <v>1.394870328286048</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240579</v>
+        <v>3.676837974240578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.02907147278793</v>
+        <v>-10.02985808660397</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.8457134526719217</v>
+        <v>-0.8460280981983375</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.807978137096867</v>
+        <v>-2.808764750912907</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.481484678498876</v>
+        <v>1.481012710209252</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.803226320068514</v>
+        <v>-9.804012933884554</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.7457963185479484</v>
+        <v>-0.7461109640743642</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.766051461509703</v>
+        <v>-2.766838075325743</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.516219756887383</v>
+        <v>1.515747788597759</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282103</v>
+        <v>3.684840248282102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.516951507745819</v>
+        <v>-9.517738121561859</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.6301472490628117</v>
+        <v>-0.6304618945892275</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.766051461509703</v>
+        <v>-2.766838075325743</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.517358901443442</v>
+        <v>1.516886933153818</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.569846795790106</v>
+        <v>-9.570633409606145</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.6486715901184184</v>
+        <v>-0.6489862356448342</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.761096115421257</v>
+        <v>-2.761882729237297</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.522965883258617</v>
+        <v>1.522493914968994</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.285938064861357</v>
+        <v>-9.286724678677396</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.5293743935082826</v>
+        <v>-0.5296890390346984</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.761096115421257</v>
+        <v>-2.761882729237297</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.528699587497254</v>
+        <v>1.52822761920763</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425331</v>
+        <v>3.72857435442533</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.038950814668405</v>
+        <v>-9.039737428484445</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.4403167558249672</v>
+        <v>-0.440631401351383</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.514108865228305</v>
+        <v>-2.514895479044345</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.66715467521916</v>
+        <v>1.666682706929536</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702416</v>
+        <v>3.747699084702415</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.775113947464336</v>
+        <v>-8.775900561280375</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.3446654902562467</v>
+        <v>-0.3449801357826625</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.514108865228305</v>
+        <v>-2.514895479044345</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.657271193906252</v>
+        <v>1.656799225616628</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906231</v>
+        <v>3.76631350390623</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.507872146595938</v>
+        <v>-8.508658760411977</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2396033304082614</v>
+        <v>-0.2399179759346772</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.514108865228305</v>
+        <v>-2.514895479044345</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.655436633406878</v>
+        <v>1.654964665117255</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781951</v>
+        <v>3.78468094578195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.232062983195453</v>
+        <v>-8.232849597011493</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.129579980021528</v>
+        <v>-0.1298946255479438</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.425089556949572</v>
+        <v>-2.425876170765611</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.708547903400658</v>
+        <v>1.708075935111034</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-7.962995395428473</v>
+        <v>-7.963782009244513</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.0212844387692428</v>
+        <v>-0.0215990842956586</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.156021969182592</v>
+        <v>-2.156808582998632</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.870656962206339</v>
+        <v>1.870184993916715</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-7.698935457105677</v>
+        <v>-7.699722070921717</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.07107922039812342</v>
+        <v>0.07076457487170762</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.891962030859796</v>
+        <v>-1.892748644675836</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.015832609038264</v>
+        <v>2.015360640748641</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-6.991855833600839</v>
+        <v>-6.992642447416879</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.3511240361397578</v>
+        <v>0.350809390613342</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.891962030859796</v>
+        <v>-1.892748644675836</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.013045575377963</v>
+        <v>2.01257360708834</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-6.742214803614887</v>
+        <v>-6.743001417430927</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.45132407202198</v>
+        <v>0.4510094264955642</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.642321000873844</v>
+        <v>-1.643107614689884</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.163173817257376</v>
+        <v>2.162701848967752</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-6.487672904273811</v>
+        <v>-6.488459518089851</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.5525076529791675</v>
+        <v>0.5521930074527517</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.387779101532769</v>
+        <v>-1.388565715348808</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.315265778082778</v>
+        <v>2.314793809793155</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.254191682044213</v>
+        <v>-6.254978295860252</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.653824570708859</v>
+        <v>0.6535099251824432</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.15429787930317</v>
+        <v>-1.15508449311921</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.46327894025839</v>
+        <v>2.462806971968766</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.07448315190034</v>
+        <v>-6.07526976571638</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.722815772453449</v>
+        <v>0.7225011269270332</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.097126375140474</v>
+        <v>-1.097912988956514</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.494689632443048</v>
+        <v>2.494217664153425</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-5.942207678269454</v>
+        <v>-5.942994292085493</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.7710934486528309</v>
+        <v>0.7707788031264151</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.9648509015095876</v>
+        <v>-0.9656375153256271</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.569422403368607</v>
+        <v>2.568950435078984</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-5.751608003596301</v>
+        <v>-5.752394617412341</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.8501483792097284</v>
+        <v>0.8498337336833126</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.7742512268364348</v>
+        <v>-0.7750378406524743</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.686597268860136</v>
+        <v>2.686125300570512</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-5.50260820491272</v>
+        <v>-5.50339481872876</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.9626546399068197</v>
+        <v>0.9623399943804039</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.7742512268364348</v>
+        <v>-0.7750378406524743</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.699503610083794</v>
+        <v>2.69903164179417</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-5.608198194685825</v>
+        <v>-5.608984808501864</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.792442714398359</v>
+        <v>0.7921280688719432</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.8798412166095391</v>
+        <v>-0.8806278304255786</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.508173686620713</v>
+        <v>2.50770171833109</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-5.626933096804422</v>
+        <v>-5.627719710620461</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.8334930954280066</v>
+        <v>0.8331784499015908</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.8798412166095391</v>
+        <v>-0.8806278304255786</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.5567180284978</v>
+        <v>2.556246060208176</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-5.350194922133609</v>
+        <v>-5.350981535949648</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.9475673772823265</v>
+        <v>0.9472527317559107</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.6980245554996133</v>
+        <v>-0.6988111693156528</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.669187037149749</v>
+        <v>2.668715068860126</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-5.223302515698538</v>
+        <v>-5.224089129514578</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.9896103536028766</v>
+        <v>0.9892957080764608</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.5711321490645433</v>
+        <v>-0.5719187628805829</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.736608494757313</v>
+        <v>2.73613652646769</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-5.035715007788612</v>
+        <v>-5.036501621604652</v>
       </c>
       <c r="E1912" t="n">
-        <v>1.057684744671754</v>
+        <v>1.057370099145338</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.5711321490645433</v>
+        <v>-0.5719187628805829</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.72964788266222</v>
+        <v>2.729175914372596</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-4.793566614334754</v>
+        <v>-4.794353228150793</v>
       </c>
       <c r="E1913" t="n">
-        <v>1.16900645643444</v>
+        <v>1.168691810908024</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.5711321490645433</v>
+        <v>-0.5719187628805829</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.744110237043363</v>
+        <v>2.74363826875374</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-4.730337242566406</v>
+        <v>-4.731123856382445</v>
       </c>
       <c r="E1914" t="n">
-        <v>1.188830325600974</v>
+        <v>1.188515680074559</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.5711321490645433</v>
+        <v>-0.5719187628805829</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.738642357502558</v>
+        <v>2.738170389212935</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-4.5438495501894</v>
+        <v>-4.544636164005439</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.260923496562354</v>
+        <v>1.260608851035938</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.3846444566875371</v>
+        <v>-0.3854310705035766</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.848033066939339</v>
+        <v>2.847561098649715</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-4.522700351285956</v>
+        <v>-4.523486965101996</v>
       </c>
       <c r="E1916" t="n">
-        <v>1.277084154361057</v>
+        <v>1.276769508834641</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.3634952577840938</v>
+        <v>-0.3642818716001333</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.86842356451873</v>
+        <v>2.867951596229107</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-4.278934909302512</v>
+        <v>-4.279721523118551</v>
       </c>
       <c r="E1917" t="n">
-        <v>1.370371039501485</v>
+        <v>1.370056393975069</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.3634952577840938</v>
+        <v>-0.3642818716001333</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.864204272865781</v>
+        <v>2.863732304576158</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-4.014906842109252</v>
+        <v>-4.015693455925291</v>
       </c>
       <c r="E1918" t="n">
-        <v>1.478106580298805</v>
+        <v>1.47779193477239</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.1616298589681402</v>
+        <v>-0.1624164727841797</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.987447826075369</v>
+        <v>2.986975857785746</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-3.765056448160177</v>
+        <v>-3.765843061976216</v>
       </c>
       <c r="E1919" t="n">
-        <v>1.570788812862137</v>
+        <v>1.570474167335722</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.1616298589681402</v>
+        <v>-0.1624164727841797</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.980189901059072</v>
+        <v>2.979717932769448</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-3.461488959156199</v>
+        <v>-3.462275572972238</v>
       </c>
       <c r="E1920" t="n">
-        <v>1.695814931984377</v>
+        <v>1.695500286457962</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.1616298589681402</v>
+        <v>-0.1624164727841797</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.98378902457972</v>
+        <v>2.983317056290097</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-3.388009050304184</v>
+        <v>-3.388795664120224</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.738534401579737</v>
+        <v>1.738219756053321</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.08814995011612581</v>
+        <v>-0.08893656393216531</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.041204475945483</v>
+        <v>3.040732507655859</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,45 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.727110450779685</v>
+        <v>3.773761647102782</v>
       </c>
       <c r="C1922" t="n">
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-3.162976050635361</v>
+        <v>-3.387851636053366</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.827568079063563</v>
+        <v>1.737617844896361</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.136883049552697</v>
+        <v>-0.08799253586530753</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.175244753363073</v>
+        <v>3.04031940211227</v>
+      </c>
+    </row>
+    <row r="1923">
+      <c r="A1923" s="2" t="n">
+        <v>45385</v>
+      </c>
+      <c r="B1923" t="n">
+        <v>3.726773608153002</v>
+      </c>
+      <c r="C1923" t="n">
+        <v>3.131420049396575</v>
+      </c>
+      <c r="D1923" t="n">
+        <v>-3.387851636053366</v>
+      </c>
+      <c r="E1923" t="n">
+        <v>1.737617844896361</v>
+      </c>
+      <c r="F1923" t="n">
+        <v>-0.08799253586530753</v>
+      </c>
+      <c r="G1923" t="n">
+        <v>3.124483846382943</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240403.xlsx
+++ b/tame_output/ON/bt/strategyON_20240403.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.5%</t>
+          <t>-73.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.2%</t>
+          <t>111.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.2%</t>
+          <t>93.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-603.0%</t>
+          <t>-602.9%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-69.9%</t>
+          <t>-68.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.2%</t>
+          <t>92.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>498.9%</t>
+          <t>499.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-500.4%</t>
+          <t>-477.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-241.6%</t>
+          <t>-241.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-152.4%</t>
+          <t>-152.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-202.5%</t>
+          <t>-193.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-25.9%</t>
+          <t>-23.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>70.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-305.5%</t>
+          <t>-305.4%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-19.0%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-232.8%</t>
+          <t>-210.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-183.7%</t>
+          <t>-183.6%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130021</v>
+        <v>3.287377576130022</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.649031488298536</v>
+        <v>-3.648244874482496</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.675996700229958</v>
+        <v>1.676311345756374</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.5962046687232554</v>
+        <v>-0.5954180549072157</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.778242918629167</v>
+        <v>2.778714886918791</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178248</v>
+        <v>3.315884374178249</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.655692428520684</v>
+        <v>-3.654905814704644</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.675105250841359</v>
+        <v>1.675419896367774</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.5962046687232554</v>
+        <v>-0.5954180549072157</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.780015845329427</v>
+        <v>2.78048781361905</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.08749822167047</v>
+        <v>-4.086711607854431</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.488715821048848</v>
+        <v>1.489030466575264</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.7326221651645224</v>
+        <v>-0.7318355513484827</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.684498234932071</v>
+        <v>2.684970203221694</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310986</v>
+        <v>3.284619513310987</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.413930750538214</v>
+        <v>-4.413144136722175</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.346427584503841</v>
+        <v>1.346742230030257</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.8150904156716705</v>
+        <v>-0.8143038018556308</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.623302059629872</v>
+        <v>2.623774027919496</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006538</v>
+        <v>3.305849539006539</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.415494901648517</v>
+        <v>-4.414708287832478</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.344382515715685</v>
+        <v>1.344697161242101</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.8150904156716705</v>
+        <v>-0.8143038018556308</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.621882651285838</v>
+        <v>2.622354619575462</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309428</v>
+        <v>3.311086391309429</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.779121146548831</v>
+        <v>-4.778334532732791</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.205419577989801</v>
+        <v>1.205734223516217</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9133120525387963</v>
+        <v>-0.9125254387227566</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.569437229399804</v>
+        <v>2.569909197689427</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970909</v>
+        <v>3.30471571697091</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.776694082020112</v>
+        <v>-4.775907468204073</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.20564491880712</v>
+        <v>1.205959564333536</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.913644834345948</v>
+        <v>-0.9128582205299083</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.568492075321344</v>
+        <v>2.568964043610968</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330526</v>
+        <v>3.300815818330527</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.18528285920079</v>
+        <v>-5.184496245384751</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.040970951949608</v>
+        <v>1.041285597476024</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.322233611526626</v>
+        <v>-1.321446997710587</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.322100353027696</v>
+        <v>2.32257232131732</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191741</v>
+        <v>3.302618194191742</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.598265343341884</v>
+        <v>-5.597478729525845</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.870963390764631</v>
+        <v>0.8712780362910468</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.322233611526626</v>
+        <v>-1.321446997710587</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.317285785499157</v>
+        <v>2.317757753788781</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108643</v>
+        <v>3.305023265108644</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.014657217628882</v>
+        <v>-6.013870603812842</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.7024006916587093</v>
+        <v>0.7027153371851251</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.322233611526626</v>
+        <v>-1.321446997710587</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.315279836108034</v>
+        <v>2.315751804397658</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097825</v>
+        <v>3.341378723097826</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.391334228158726</v>
+        <v>-6.390547614342687</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.5619885781154506</v>
+        <v>0.5623032236418664</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.322233611526626</v>
+        <v>-1.321446997710587</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.325538526776713</v>
+        <v>2.326010495066337</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094121</v>
+        <v>3.374439043094122</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.405049092483837</v>
+        <v>-6.404262478667798</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.5526021975311011</v>
+        <v>0.5529168430575169</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.322233611526626</v>
+        <v>-1.321446997710587</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.321638091922408</v>
+        <v>2.322110060212032</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119929</v>
+        <v>3.405960511199291</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.717873891728817</v>
+        <v>-6.717087277912777</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.4258771978881102</v>
+        <v>0.426191843414526</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.322233611526626</v>
+        <v>-1.321446997710587</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.320043011977409</v>
+        <v>2.320514980267033</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969599</v>
+        <v>3.4246333549696</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.722686930194154</v>
+        <v>-6.721900316378115</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.4277309584311837</v>
+        <v>0.4280456039575995</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.323780246229412</v>
+        <v>-1.322993632413373</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.322894007084946</v>
+        <v>2.323365975374569</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923092</v>
+        <v>3.419979433923093</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.15603603830439</v>
+        <v>-7.155249424488351</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.2503650106526862</v>
+        <v>0.250679656179102</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.323780246229412</v>
+        <v>-1.322993632413373</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.318867702550543</v>
+        <v>2.319339670840167</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297754</v>
+        <v>3.458100091297755</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.539037427047021</v>
+        <v>-7.538250813230982</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.09706235383404938</v>
+        <v>0.09737699936046518</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.323780246229412</v>
+        <v>-1.322993632413373</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.318765601228959</v>
+        <v>2.319237569518583</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317621</v>
+        <v>3.447750501317622</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.914022753218299</v>
+        <v>-7.913236139402259</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.05036026066303112</v>
+        <v>-0.05004561513661532</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.69876557240069</v>
+        <v>-1.69797895858465</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.096345921497623</v>
+        <v>2.096817889787246</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737175</v>
+        <v>3.503515506737176</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.273553075722301</v>
+        <v>-8.272766461906262</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.1888220863665815</v>
+        <v>-0.1885074408401657</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.69876557240069</v>
+        <v>-1.69797895858465</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.101696224795673</v>
+        <v>2.102168193085296</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341318</v>
+        <v>3.503170282341319</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.599953104387314</v>
+        <v>-8.599166490571275</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.3114660778754095</v>
+        <v>-0.3111514323489937</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.025165601065702</v>
+        <v>-2.024378987249663</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.913772227553842</v>
+        <v>1.914244195843466</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.593476957593754</v>
+        <v>-8.592690343777715</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.3058338685362165</v>
+        <v>-0.3055192230098007</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.018689454272143</v>
+        <v>-2.017902840456103</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.920699666251747</v>
+        <v>1.921171634541371</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.589786032637344</v>
+        <v>-8.588999418821304</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.3043574985536526</v>
+        <v>-0.3040428530272368</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.018689454272143</v>
+        <v>-2.017902840456103</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.920699666251747</v>
+        <v>1.921171634541371</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.794044207967207</v>
+        <v>-8.793257594151168</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3805475715669555</v>
+        <v>-0.3802329260405397</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.146328398886132</v>
+        <v>-2.145541785070092</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.849629496601996</v>
+        <v>1.85010146489162</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.954683234455572</v>
+        <v>-8.953896620639533</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.4403206276778655</v>
+        <v>-0.4400059821514497</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.261061871888527</v>
+        <v>-2.260275258072488</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.785271967284995</v>
+        <v>1.785743935574619</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.881213402788124</v>
+        <v>-8.880426788972084</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.3955609935174649</v>
+        <v>-0.3952463479910491</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.187592040221079</v>
+        <v>-2.186805426405039</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.844725567778885</v>
+        <v>1.845197536068509</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.056337820174667</v>
+        <v>-9.055551206358627</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.4510555397245652</v>
+        <v>-0.4507408941981494</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.362716457607623</v>
+        <v>-2.361929843791583</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.754206138094476</v>
+        <v>1.754678106384099</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587501888027</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.290789914189157</v>
+        <v>-9.290003300373117</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.5520555422319573</v>
+        <v>-0.5517408967055415</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.362716457607623</v>
+        <v>-2.361929843791583</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.74698697319288</v>
+        <v>1.747458941482503</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234395</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.578593758726395</v>
+        <v>-9.577807144910356</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.673849270820829</v>
+        <v>-0.6735346252944132</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.650520302144861</v>
+        <v>-2.649733688328821</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.56763247569656</v>
+        <v>1.568104443986184</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.80841820589022</v>
+        <v>-9.807631592074181</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.7646632598478025</v>
+        <v>-0.7643486143213867</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.813167839215021</v>
+        <v>-2.812381225398982</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.47115974329302</v>
+        <v>1.471631711582644</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767398</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.04044712562648</v>
+        <v>-10.03966051181044</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.8547810991131928</v>
+        <v>-0.854466453586777</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.875180536403445</v>
+        <v>-2.874393922587405</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.436645853609081</v>
+        <v>1.437117821898705</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.988431611657669</v>
+        <v>-9.987644997841629</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.8299845578392664</v>
+        <v>-0.8296699123128506</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.875180536403445</v>
+        <v>-2.874393922587405</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.440636189295482</v>
+        <v>1.441108157585106</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.13010345338179</v>
+        <v>-10.12931683956575</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.8881285214276566</v>
+        <v>-0.8878138759012408</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.875180536403445</v>
+        <v>-2.874393922587405</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.43916096239674</v>
+        <v>1.439632930686364</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.22901019384106</v>
+        <v>-10.22822358002503</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.9126378074464943</v>
+        <v>-0.9123231619200785</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.97408727686272</v>
+        <v>-2.97330066304668</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.394870328286048</v>
+        <v>1.395342296575671</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240578</v>
+        <v>3.676837974240579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.02985808660397</v>
+        <v>-10.02907147278793</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.8460280981983375</v>
+        <v>-0.8457134526719217</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.808764750912907</v>
+        <v>-2.807978137096867</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.481012710209252</v>
+        <v>1.481484678498876</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.804012933884554</v>
+        <v>-9.803226320068514</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.7461109640743642</v>
+        <v>-0.7457963185479484</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.766838075325743</v>
+        <v>-2.766051461509703</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.515747788597759</v>
+        <v>1.516219756887383</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282102</v>
+        <v>3.684840248282103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.517738121561859</v>
+        <v>-9.516951507745819</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.6304618945892275</v>
+        <v>-0.6301472490628117</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.766838075325743</v>
+        <v>-2.766051461509703</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.516886933153818</v>
+        <v>1.517358901443442</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.570633409606145</v>
+        <v>-9.569846795790106</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.6489862356448342</v>
+        <v>-0.6486715901184184</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.761882729237297</v>
+        <v>-2.761096115421257</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.522493914968994</v>
+        <v>1.522965883258617</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.286724678677396</v>
+        <v>-9.285938064861357</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.5296890390346984</v>
+        <v>-0.5293743935082826</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.761882729237297</v>
+        <v>-2.761096115421257</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.52822761920763</v>
+        <v>1.528699587497254</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.039737428484445</v>
+        <v>-9.038950814668405</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.440631401351383</v>
+        <v>-0.4403167558249672</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.514895479044345</v>
+        <v>-2.514108865228305</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.666682706929536</v>
+        <v>1.66715467521916</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.775900561280375</v>
+        <v>-8.775113947464336</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.3449801357826625</v>
+        <v>-0.3446654902562467</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.514895479044345</v>
+        <v>-2.514108865228305</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.656799225616628</v>
+        <v>1.657271193906252</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.508658760411977</v>
+        <v>-8.507872146595938</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2399179759346772</v>
+        <v>-0.2396033304082614</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.514895479044345</v>
+        <v>-2.514108865228305</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.654964665117255</v>
+        <v>1.655436633406878</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.232849597011493</v>
+        <v>-8.232062983195453</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1298946255479438</v>
+        <v>-0.129579980021528</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.425876170765611</v>
+        <v>-2.425089556949572</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.708075935111034</v>
+        <v>1.708547903400658</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-7.963782009244513</v>
+        <v>-7.962995395428473</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.0215990842956586</v>
+        <v>-0.0212844387692428</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.156808582998632</v>
+        <v>-2.156021969182592</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.870184993916715</v>
+        <v>1.870656962206339</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-7.699722070921717</v>
+        <v>-7.698935457105677</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.07076457487170762</v>
+        <v>0.07107922039812342</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.892748644675836</v>
+        <v>-1.891962030859796</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.015360640748641</v>
+        <v>2.015832609038264</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-6.992642447416879</v>
+        <v>-6.991855833600839</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.350809390613342</v>
+        <v>0.3511240361397578</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.892748644675836</v>
+        <v>-1.891962030859796</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.01257360708834</v>
+        <v>2.013045575377963</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-6.743001417430927</v>
+        <v>-6.742214803614887</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.4510094264955642</v>
+        <v>0.45132407202198</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.643107614689884</v>
+        <v>-1.642321000873844</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.162701848967752</v>
+        <v>2.163173817257376</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-6.488459518089851</v>
+        <v>-6.487672904273811</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.5521930074527517</v>
+        <v>0.5525076529791675</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.388565715348808</v>
+        <v>-1.387779101532769</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.314793809793155</v>
+        <v>2.315265778082778</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.254978295860252</v>
+        <v>-6.254191682044213</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.6535099251824432</v>
+        <v>0.653824570708859</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.15508449311921</v>
+        <v>-1.15429787930317</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.462806971968766</v>
+        <v>2.46327894025839</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.07526976571638</v>
+        <v>-6.07448315190034</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.7225011269270332</v>
+        <v>0.722815772453449</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.097912988956514</v>
+        <v>-1.097126375140474</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.494217664153425</v>
+        <v>2.494689632443048</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-5.942994292085493</v>
+        <v>-5.942207678269454</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.7707788031264151</v>
+        <v>0.7710934486528309</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.9656375153256271</v>
+        <v>-0.9648509015095876</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.568950435078984</v>
+        <v>2.569422403368607</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-5.752394617412341</v>
+        <v>-5.751608003596301</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.8498337336833126</v>
+        <v>0.8501483792097284</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.7750378406524743</v>
+        <v>-0.7742512268364348</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.686125300570512</v>
+        <v>2.686597268860136</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-5.50339481872876</v>
+        <v>-5.50260820491272</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.9623399943804039</v>
+        <v>0.9626546399068197</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.7750378406524743</v>
+        <v>-0.7742512268364348</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.69903164179417</v>
+        <v>2.699503610083794</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-5.608984808501864</v>
+        <v>-5.608198194685825</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.7921280688719432</v>
+        <v>0.792442714398359</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.8806278304255786</v>
+        <v>-0.8798412166095391</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.50770171833109</v>
+        <v>2.508173686620713</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-5.627719710620461</v>
+        <v>-5.626933096804422</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.8331784499015908</v>
+        <v>0.8334930954280066</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.8806278304255786</v>
+        <v>-0.8798412166095391</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.556246060208176</v>
+        <v>2.5567180284978</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-5.350981535949648</v>
+        <v>-5.350194922133609</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.9472527317559107</v>
+        <v>0.9475673772823265</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.6988111693156528</v>
+        <v>-0.6980245554996133</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.668715068860126</v>
+        <v>2.669187037149749</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-5.224089129514578</v>
+        <v>-5.223302515698538</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.9892957080764608</v>
+        <v>0.9896103536028766</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.5719187628805829</v>
+        <v>-0.5711321490645433</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.73613652646769</v>
+        <v>2.736608494757313</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-5.036501621604652</v>
+        <v>-5.035715007788612</v>
       </c>
       <c r="E1912" t="n">
-        <v>1.057370099145338</v>
+        <v>1.057684744671754</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.5719187628805829</v>
+        <v>-0.5711321490645433</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.729175914372596</v>
+        <v>2.72964788266222</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-4.794353228150793</v>
+        <v>-4.793566614334754</v>
       </c>
       <c r="E1913" t="n">
-        <v>1.168691810908024</v>
+        <v>1.16900645643444</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.5719187628805829</v>
+        <v>-0.5711321490645433</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.74363826875374</v>
+        <v>2.744110237043363</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-4.731123856382445</v>
+        <v>-4.730337242566406</v>
       </c>
       <c r="E1914" t="n">
-        <v>1.188515680074559</v>
+        <v>1.188830325600974</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.5719187628805829</v>
+        <v>-0.5711321490645433</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.738170389212935</v>
+        <v>2.738642357502558</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-4.544636164005439</v>
+        <v>-4.5438495501894</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.260608851035938</v>
+        <v>1.260923496562354</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.3854310705035766</v>
+        <v>-0.3846444566875371</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.847561098649715</v>
+        <v>2.848033066939339</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-4.523486965101996</v>
+        <v>-4.522700351285956</v>
       </c>
       <c r="E1916" t="n">
-        <v>1.276769508834641</v>
+        <v>1.277084154361057</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.3642818716001333</v>
+        <v>-0.3634952577840938</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.867951596229107</v>
+        <v>2.86842356451873</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-4.279721523118551</v>
+        <v>-4.278934909302512</v>
       </c>
       <c r="E1917" t="n">
-        <v>1.370056393975069</v>
+        <v>1.370371039501485</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.3642818716001333</v>
+        <v>-0.3634952577840938</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.863732304576158</v>
+        <v>2.864204272865781</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-4.015693455925291</v>
+        <v>-4.014906842109252</v>
       </c>
       <c r="E1918" t="n">
-        <v>1.47779193477239</v>
+        <v>1.478106580298805</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.1624164727841797</v>
+        <v>-0.1616298589681402</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.986975857785746</v>
+        <v>2.987447826075369</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-3.765843061976216</v>
+        <v>-3.765056448160177</v>
       </c>
       <c r="E1919" t="n">
-        <v>1.570474167335722</v>
+        <v>1.570788812862137</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.1624164727841797</v>
+        <v>-0.1616298589681402</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.979717932769448</v>
+        <v>2.980189901059072</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-3.462275572972238</v>
+        <v>-3.461488959156199</v>
       </c>
       <c r="E1920" t="n">
-        <v>1.695500286457962</v>
+        <v>1.695814931984377</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.1624164727841797</v>
+        <v>-0.1616298589681402</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.983317056290097</v>
+        <v>2.98378902457972</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-3.388795664120224</v>
+        <v>-3.388009050304184</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.738219756053321</v>
+        <v>1.738534401579737</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.08893656393216531</v>
+        <v>-0.08814995011612581</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.040732507655859</v>
+        <v>3.041204475945483</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102782</v>
+        <v>3.773761647102783</v>
       </c>
       <c r="C1922" t="n">
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-3.387851636053366</v>
+        <v>-3.162976050635361</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.737617844896361</v>
+        <v>1.827568079063563</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.08799253586530753</v>
+        <v>0.136883049552697</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.04031940211227</v>
+        <v>3.175244753363073</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,19 +45774,19 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.726773608153002</v>
+        <v>3.726773608153003</v>
       </c>
       <c r="C1923" t="n">
         <v>3.131420049396575</v>
       </c>
       <c r="D1923" t="n">
-        <v>-3.387851636053366</v>
+        <v>-3.162976050635361</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.737617844896361</v>
+        <v>1.827568079063563</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.08799253586530753</v>
+        <v>0.136883049552697</v>
       </c>
       <c r="G1923" t="n">
         <v>3.124483846382943</v>

--- a/tame_output/ON/bt/strategyON_20240403.xlsx
+++ b/tame_output/ON/bt/strategyON_20240403.xlsx
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097826</v>
+        <v>3.341378723097825</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094122</v>
+        <v>3.374439043094121</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199291</v>
+        <v>3.40596051119929</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.4246333549696</v>
+        <v>3.424633354969599</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923093</v>
+        <v>3.419979433923092</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297755</v>
+        <v>3.458100091297754</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317622</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737176</v>
+        <v>3.503515506737174</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341319</v>
+        <v>3.503170282341317</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776682</v>
+        <v>3.500446096776681</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611696</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910628</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.492098065767397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792544</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.600034689628919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410719</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240579</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085281</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282103</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116218</v>
+        <v>3.710931958116217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>

--- a/tame_output/ON/bt/strategyON_20240403.xlsx
+++ b/tame_output/ON/bt/strategyON_20240403.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>14.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>-1.8%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.5%</t>
+          <t>-75.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.6%</t>
+          <t>112.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.9%</t>
+          <t>130.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.2%</t>
+          <t>92.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-602.9%</t>
+          <t>-635.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.3%</t>
+          <t>-50.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-68.7%</t>
+          <t>-70.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.6%</t>
+          <t>92.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>499.6%</t>
+          <t>495.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-477.9%</t>
+          <t>-511.9%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-241.5%</t>
+          <t>-254.6%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.4%</t>
+          <t>-39.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-152.5%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>-18.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-193.5%</t>
+          <t>-206.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-23.0%</t>
+          <t>-20.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-305.4%</t>
+          <t>-306.6%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.7%</t>
+          <t>-33.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-160.9%</t>
+          <t>-161.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-210.3%</t>
+          <t>-190.9%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.7%</t>
+          <t>96.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-183.6%</t>
+          <t>-184.4%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,42 +1466,42 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.0%</t>
+          <t>-29.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-133.6%</t>
+          <t>-116.4%</t>
         </is>
       </c>
     </row>
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.648244874482496</v>
+        <v>-3.660017067431099</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.676311345756374</v>
+        <v>1.671602468576933</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.5954180549072157</v>
+        <v>-0.6071902478558189</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.778714886918791</v>
+        <v>2.771651571149629</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178249</v>
+        <v>3.315884374178248</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.654905814704644</v>
+        <v>-3.981368475249438</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.675419896367774</v>
+        <v>1.544834832149857</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.5954180549072157</v>
+        <v>-0.6071902478558189</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.78048781361905</v>
+        <v>2.773424497849888</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.086711607854431</v>
+        <v>-4.413174268399226</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.489030466575264</v>
+        <v>1.358445402357346</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.7318355513484827</v>
+        <v>-0.7436077442970859</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.684970203221694</v>
+        <v>2.677906887452532</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.413144136722175</v>
+        <v>-4.73960679726697</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.346742230030257</v>
+        <v>1.216157165812339</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.8143038018556308</v>
+        <v>-0.826075994804234</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.623774027919496</v>
+        <v>2.616710712150335</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.414708287832478</v>
+        <v>-4.741170948377273</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.344697161242101</v>
+        <v>1.214112097024183</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.8143038018556308</v>
+        <v>-0.826075994804234</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.622354619575462</v>
+        <v>2.6152913038063</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.778334532732791</v>
+        <v>-5.104797193277586</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.205734223516217</v>
+        <v>1.0751491592983</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9125254387227566</v>
+        <v>-0.9242976316713598</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.569909197689427</v>
+        <v>2.562845881920266</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.775907468204073</v>
+        <v>-5.102370128748868</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.205959564333536</v>
+        <v>1.075374500115618</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.9128582205299083</v>
+        <v>-0.9246304134785115</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.568964043610968</v>
+        <v>2.561900727841806</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.184496245384751</v>
+        <v>-5.510958905929547</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.041285597476024</v>
+        <v>0.9107005332581055</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.321446997710587</v>
+        <v>-1.33321919065919</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.32257232131732</v>
+        <v>2.315509005548158</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.597478729525845</v>
+        <v>-5.923941390070641</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.8712780362910468</v>
+        <v>0.7406929720731288</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.321446997710587</v>
+        <v>-1.33321919065919</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.317757753788781</v>
+        <v>2.310694438019619</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.013870603812842</v>
+        <v>-6.340333264357638</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.7027153371851251</v>
+        <v>0.5721302729672071</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.321446997710587</v>
+        <v>-1.33321919065919</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.315751804397658</v>
+        <v>2.308688488628496</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097825</v>
+        <v>3.341378723097826</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.390547614342687</v>
+        <v>-6.717010274887483</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.5623032236418664</v>
+        <v>0.4317181594239483</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.321446997710587</v>
+        <v>-1.33321919065919</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.326010495066337</v>
+        <v>2.318947179297175</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094121</v>
+        <v>3.374439043094122</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.404262478667798</v>
+        <v>-6.730725139212594</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.5529168430575169</v>
+        <v>0.4223317788395988</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.321446997710587</v>
+        <v>-1.33321919065919</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.322110060212032</v>
+        <v>2.31504674444287</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119929</v>
+        <v>3.405960511199291</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.717087277912777</v>
+        <v>-7.043549938457573</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.426191843414526</v>
+        <v>0.2956067791966079</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.321446997710587</v>
+        <v>-1.33321919065919</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.320514980267033</v>
+        <v>2.313451664497871</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969599</v>
+        <v>3.4246333549696</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.721900316378115</v>
+        <v>-7.048362976922911</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.4280456039575995</v>
+        <v>0.2974605397396815</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.322993632413373</v>
+        <v>-1.334765825361976</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.323365975374569</v>
+        <v>2.316302659605408</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923092</v>
+        <v>3.419979433923093</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.155249424488351</v>
+        <v>-7.481712085033147</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.250679656179102</v>
+        <v>0.120094591961184</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.322993632413373</v>
+        <v>-1.334765825361976</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.319339670840167</v>
+        <v>2.312276355071005</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297754</v>
+        <v>3.458100091297755</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.538250813230982</v>
+        <v>-7.864713473775778</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.09737699936046518</v>
+        <v>-0.03320806485745287</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.322993632413373</v>
+        <v>-1.334765825361976</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.319237569518583</v>
+        <v>2.312174253749421</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317622</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.913236139402259</v>
+        <v>-8.239698799947055</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.05004561513661532</v>
+        <v>-0.1806306793545334</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.69797895858465</v>
+        <v>-1.709751151533253</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.096817889787246</v>
+        <v>2.089754574018084</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737174</v>
+        <v>3.503515506737176</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.272766461906262</v>
+        <v>-8.599229122451057</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.1885074408401657</v>
+        <v>-0.3190925050580837</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.69797895858465</v>
+        <v>-1.709751151533253</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.102168193085296</v>
+        <v>2.095104877316134</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341317</v>
+        <v>3.503170282341319</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.599166490571275</v>
+        <v>-8.92562915111607</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.3111514323489937</v>
+        <v>-0.4417364965669117</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.024378987249663</v>
+        <v>-2.036151180198266</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.914244195843466</v>
+        <v>1.907180880074304</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776681</v>
+        <v>3.500446096776682</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.592690343777715</v>
+        <v>-8.91915300432251</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.3055192230098007</v>
+        <v>-0.4361042872277188</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.017902840456103</v>
+        <v>-2.029675033404706</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.921171634541371</v>
+        <v>1.914108318772209</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.588999418821304</v>
+        <v>-8.915462079366099</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.3040428530272368</v>
+        <v>-0.4346279172451548</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.017902840456103</v>
+        <v>-2.029675033404706</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.921171634541371</v>
+        <v>1.914108318772209</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.793257594151168</v>
+        <v>-9.119720254695963</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3802329260405397</v>
+        <v>-0.5108179902584578</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.145541785070092</v>
+        <v>-2.157313978018695</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.85010146489162</v>
+        <v>1.843038149122458</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.953896620639533</v>
+        <v>-9.280359281184328</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.4400059821514497</v>
+        <v>-0.5705910463693677</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.260275258072488</v>
+        <v>-2.272047451021091</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.785743935574619</v>
+        <v>1.778680619805457</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910628</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.880426788972084</v>
+        <v>-9.206889449516879</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.3952463479910491</v>
+        <v>-0.5258314122089671</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.186805426405039</v>
+        <v>-2.198577619353642</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.845197536068509</v>
+        <v>1.838134220299347</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.055551206358627</v>
+        <v>-9.382013866903423</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.4507408941981494</v>
+        <v>-0.5813259584160675</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.361929843791583</v>
+        <v>-2.373702036740186</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.754678106384099</v>
+        <v>1.747614790614937</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880269</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.290003300373117</v>
+        <v>-9.616465960917912</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.5517408967055415</v>
+        <v>-0.6823259609234595</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.361929843791583</v>
+        <v>-2.373702036740186</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.747458941482503</v>
+        <v>1.740395625713341</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234394</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.577807144910356</v>
+        <v>-9.904269805455151</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.6735346252944132</v>
+        <v>-0.8041196895123313</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.649733688328821</v>
+        <v>-2.661505881277424</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.568104443986184</v>
+        <v>1.561041128217022</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860584</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.807631592074181</v>
+        <v>-10.13409425261898</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.7643486143213867</v>
+        <v>-0.8949336785393047</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.812381225398982</v>
+        <v>-2.824153418347585</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.471631711582644</v>
+        <v>1.464568395813482</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767397</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.03966051181044</v>
+        <v>-10.36612317235524</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.854466453586777</v>
+        <v>-0.985051517804695</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.874393922587405</v>
+        <v>-2.886166115536008</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.437117821898705</v>
+        <v>1.430054506129543</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.987644997841629</v>
+        <v>-10.31410765838642</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.8296699123128506</v>
+        <v>-0.9602549765307691</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.874393922587405</v>
+        <v>-2.886166115536008</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.441108157585106</v>
+        <v>1.434044841815944</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628919</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.12931683956575</v>
+        <v>-10.45577950011054</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.8878138759012408</v>
+        <v>-1.018398940119159</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.874393922587405</v>
+        <v>-2.886166115536008</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.439632930686364</v>
+        <v>1.432569614917202</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.22822358002503</v>
+        <v>-10.55468624056982</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.9123231619200785</v>
+        <v>-1.042908226137996</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.97330066304668</v>
+        <v>-2.985072855995284</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.395342296575671</v>
+        <v>1.388278980806509</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676837974240579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.02907147278793</v>
+        <v>-10.35553413333272</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.8457134526719217</v>
+        <v>-0.9762985168898397</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.807978137096867</v>
+        <v>-2.81975033004547</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.481484678498876</v>
+        <v>1.474421362729714</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.803226320068514</v>
+        <v>-10.12968898061331</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.7457963185479484</v>
+        <v>-0.8763813827658669</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.766051461509703</v>
+        <v>-2.777823654458307</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.516219756887383</v>
+        <v>1.509156441118221</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.684840248282103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.516951507745819</v>
+        <v>-9.843414168290614</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.6301472490628117</v>
+        <v>-0.7607323132807298</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.766051461509703</v>
+        <v>-2.777823654458307</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.517358901443442</v>
+        <v>1.51029558567428</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116217</v>
+        <v>3.710931958116218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.569846795790106</v>
+        <v>-9.896309456334901</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.6486715901184184</v>
+        <v>-0.7792566543363364</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.761096115421257</v>
+        <v>-2.772868308369861</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.522965883258617</v>
+        <v>1.515902567489455</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.285938064861357</v>
+        <v>-9.832240041437185</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.5293743935082826</v>
+        <v>-0.7478951841386134</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.761096115421257</v>
+        <v>-2.772868308369861</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.528699587497254</v>
+        <v>1.521636271728092</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.72857435442533</v>
+        <v>3.728574354425331</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.038950814668405</v>
+        <v>-9.585252791244233</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.4403167558249672</v>
+        <v>-0.658837546455298</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.514108865228305</v>
+        <v>-2.525881058176909</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.66715467521916</v>
+        <v>1.660091359449998</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702415</v>
+        <v>3.747699084702416</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.775113947464336</v>
+        <v>-9.321415924040164</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.3446654902562467</v>
+        <v>-0.563186280886578</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.514108865228305</v>
+        <v>-2.525881058176909</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.657271193906252</v>
+        <v>1.65020787813709</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.76631350390623</v>
+        <v>3.766313503906231</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.507872146595938</v>
+        <v>-9.054174123171766</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2396033304082614</v>
+        <v>-0.4581241210385927</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.514108865228305</v>
+        <v>-2.525881058176909</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.655436633406878</v>
+        <v>1.648373317637716</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468094578195</v>
+        <v>3.784680945781951</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.232062983195453</v>
+        <v>-8.778364959771281</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.129579980021528</v>
+        <v>-0.3481007706518593</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.425089556949572</v>
+        <v>-2.436861749898175</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.708547903400658</v>
+        <v>1.701484587631496</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-7.962995395428473</v>
+        <v>-8.509297372004301</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.0212844387692428</v>
+        <v>-0.239805229399574</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.156021969182592</v>
+        <v>-2.167794162131196</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.870656962206339</v>
+        <v>1.863593646437177</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-7.698935457105677</v>
+        <v>-8.245237433681504</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.07107922039812342</v>
+        <v>-0.1474415702322074</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.891962030859796</v>
+        <v>-1.9037342238084</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.015832609038264</v>
+        <v>2.008769293269102</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-6.991855833600839</v>
+        <v>-7.538157810176666</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.3511240361397578</v>
+        <v>0.132603245509427</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.891962030859796</v>
+        <v>-1.9037342238084</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.013045575377963</v>
+        <v>2.005982259608801</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-6.742214803614887</v>
+        <v>-7.288516780190714</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.45132407202198</v>
+        <v>0.2328032813916492</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.642321000873844</v>
+        <v>-1.654093193822448</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.163173817257376</v>
+        <v>2.156110501488214</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-6.487672904273811</v>
+        <v>-7.033974880849639</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.5525076529791675</v>
+        <v>0.3339868623488362</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.387779101532769</v>
+        <v>-1.399551294481372</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.315265778082778</v>
+        <v>2.308202462313616</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.254191682044213</v>
+        <v>-6.800493658620041</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.653824570708859</v>
+        <v>0.4353037800785282</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.15429787930317</v>
+        <v>-1.166070072251774</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.46327894025839</v>
+        <v>2.456215624489228</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.07448315190034</v>
+        <v>-6.620785128476168</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.722815772453449</v>
+        <v>0.5042949818231177</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.097126375140474</v>
+        <v>-1.108898568089078</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.494689632443048</v>
+        <v>2.487626316673886</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-5.942207678269454</v>
+        <v>-6.488509654845282</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.7710934486528309</v>
+        <v>0.5525726580224997</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.9648509015095876</v>
+        <v>-0.9766230944581911</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.569422403368607</v>
+        <v>2.562359087599445</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-5.751608003596301</v>
+        <v>-6.297909980172129</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.8501483792097284</v>
+        <v>0.6316275885793972</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.7742512268364348</v>
+        <v>-0.7860234197850382</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.686597268860136</v>
+        <v>2.679533953090973</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-5.50260820491272</v>
+        <v>-6.048910181488548</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.9626546399068197</v>
+        <v>0.7441338492764884</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.7742512268364348</v>
+        <v>-0.7860234197850382</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.699503610083794</v>
+        <v>2.692440294314632</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-5.608198194685825</v>
+        <v>-6.154500171261652</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.792442714398359</v>
+        <v>0.5739219237680278</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.8798412166095391</v>
+        <v>-0.8916134095581425</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.508173686620713</v>
+        <v>2.501110370851551</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-5.626933096804422</v>
+        <v>-6.173235073380249</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.8334930954280066</v>
+        <v>0.6149723047976754</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.8798412166095391</v>
+        <v>-0.8916134095581425</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.5567180284978</v>
+        <v>2.549654712728637</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-5.350194922133609</v>
+        <v>-5.896496898709437</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.9475673772823265</v>
+        <v>0.7290465866519953</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.6980245554996133</v>
+        <v>-0.7097967484482167</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.669187037149749</v>
+        <v>2.662123721380588</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-5.223302515698538</v>
+        <v>-5.769604492274366</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.9896103536028766</v>
+        <v>0.7710895629725454</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.5711321490645433</v>
+        <v>-0.5829043420131468</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.736608494757313</v>
+        <v>2.729545178988151</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-5.035715007788612</v>
+        <v>-5.58201698436444</v>
       </c>
       <c r="E1912" t="n">
-        <v>1.057684744671754</v>
+        <v>0.8391639540414229</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.5711321490645433</v>
+        <v>-0.5829043420131468</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.72964788266222</v>
+        <v>2.722584566893058</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-4.793566614334754</v>
+        <v>-5.339868590910582</v>
       </c>
       <c r="E1913" t="n">
-        <v>1.16900645643444</v>
+        <v>0.9504856658041092</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.5711321490645433</v>
+        <v>-0.5829043420131468</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.744110237043363</v>
+        <v>2.737046921274201</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-4.730337242566406</v>
+        <v>-5.276639219142234</v>
       </c>
       <c r="E1914" t="n">
-        <v>1.188830325600974</v>
+        <v>0.9703095349706432</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.5711321490645433</v>
+        <v>-0.5829043420131468</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.738642357502558</v>
+        <v>2.731579041733396</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-4.5438495501894</v>
+        <v>-5.090151526765228</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.260923496562354</v>
+        <v>1.042402705932023</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.3846444566875371</v>
+        <v>-0.3964166496361405</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.848033066939339</v>
+        <v>2.840969751170177</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-4.522700351285956</v>
+        <v>-5.069002327861784</v>
       </c>
       <c r="E1916" t="n">
-        <v>1.277084154361057</v>
+        <v>1.058563363730725</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.3634952577840938</v>
+        <v>-0.3752674507326972</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.86842356451873</v>
+        <v>2.861360248749568</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-4.278934909302512</v>
+        <v>-4.82523688587834</v>
       </c>
       <c r="E1917" t="n">
-        <v>1.370371039501485</v>
+        <v>1.151850248871154</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.3634952577840938</v>
+        <v>-0.3752674507326972</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.864204272865781</v>
+        <v>2.857140957096619</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-4.014906842109252</v>
+        <v>-4.561208818685079</v>
       </c>
       <c r="E1918" t="n">
-        <v>1.478106580298805</v>
+        <v>1.259585789668474</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.1616298589681402</v>
+        <v>-0.1734020519167436</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.987447826075369</v>
+        <v>2.980384510306207</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-3.765056448160177</v>
+        <v>-4.311358424736005</v>
       </c>
       <c r="E1919" t="n">
-        <v>1.570788812862137</v>
+        <v>1.352268022231806</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.1616298589681402</v>
+        <v>-0.1734020519167436</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.980189901059072</v>
+        <v>2.97312658528991</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-3.461488959156199</v>
+        <v>-4.007790935732027</v>
       </c>
       <c r="E1920" t="n">
-        <v>1.695814931984377</v>
+        <v>1.477294141354046</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.1616298589681402</v>
+        <v>-0.1734020519167436</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.98378902457972</v>
+        <v>2.976725708810558</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-3.388009050304184</v>
+        <v>-3.934311026880013</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.738534401579737</v>
+        <v>1.520013610949406</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.08814995011612581</v>
+        <v>-0.09992214306472924</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.041204475945483</v>
+        <v>3.034141160176321</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102783</v>
+        <v>3.773761647102782</v>
       </c>
       <c r="C1922" t="n">
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-3.162976050635361</v>
+        <v>-3.70927802721119</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.827568079063563</v>
+        <v>1.609047288433232</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.136883049552697</v>
+        <v>0.1251108566040936</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.175244753363073</v>
+        <v>3.168181437593911</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.726773608153003</v>
+        <v>3.427626402812001</v>
       </c>
       <c r="C1923" t="n">
-        <v>3.131420049396575</v>
+        <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-3.162976050635361</v>
+        <v>-3.503730327075221</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.827568079063563</v>
+        <v>1.695961169541937</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.136883049552697</v>
+        <v>0.3306585567400623</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.124483846382943</v>
+        <v>3.29620485872981</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240403.xlsx
+++ b/tame_output/ON/bt/strategyON_20240403.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.5%</t>
+          <t>-74.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>112.3%</t>
+          <t>112.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>130.7%</t>
+          <t>130.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.5%</t>
+          <t>93.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-635.5%</t>
+          <t>-634.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.7%</t>
+          <t>-69.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>93.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>495.6%</t>
+          <t>495.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-511.9%</t>
+          <t>-488.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-254.6%</t>
+          <t>-254.1%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-39.4%</t>
+          <t>-39.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>119.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-18.3%</t>
+          <t>-18.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-206.6%</t>
+          <t>-197.4%</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-190.9%</t>
+          <t>-191.0%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130022</v>
+        <v>3.287377576130021</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.981368475249438</v>
+        <v>-3.96925117042715</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.544834832149857</v>
+        <v>1.549681754078772</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.6071902478558189</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.413174268399226</v>
+        <v>-4.401056963576938</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.358445402357346</v>
+        <v>1.363292324286261</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.7436077442970859</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.73960679726697</v>
+        <v>-4.727489492444682</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.216157165812339</v>
+        <v>1.221004087741254</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.826075994804234</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006539</v>
+        <v>3.305849539006538</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.741170948377273</v>
+        <v>-4.729053643554985</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.214112097024183</v>
+        <v>1.218959018953099</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.826075994804234</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.104797193277586</v>
+        <v>-5.092679888455298</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.0751491592983</v>
+        <v>1.079996081227215</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.9242976316713598</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.102370128748868</v>
+        <v>-5.09025282392658</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.075374500115618</v>
+        <v>1.080221422044533</v>
       </c>
       <c r="F1863" t="n">
         <v>-0.9246304134785115</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.510958905929547</v>
+        <v>-5.498841601107259</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.9107005332581055</v>
+        <v>0.9155474551870211</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.33321919065919</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.923941390070641</v>
+        <v>-5.911824085248353</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.7406929720731288</v>
+        <v>0.7455398940020439</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.33321919065919</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.340333264357638</v>
+        <v>-6.32821595953535</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.5721302729672071</v>
+        <v>0.5769771948961222</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.33321919065919</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.717010274887483</v>
+        <v>-6.704892970065194</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.4317181594239483</v>
+        <v>0.4365650813528634</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.33321919065919</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.730725139212594</v>
+        <v>-6.718607834390306</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.4223317788395988</v>
+        <v>0.4271787007685144</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.33321919065919</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.043549938457573</v>
+        <v>-7.031432633635285</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.2956067791966079</v>
+        <v>0.3004537011255235</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.33321919065919</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.048362976922911</v>
+        <v>-7.036245672100622</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.2974605397396815</v>
+        <v>0.3023074616685966</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.334765825361976</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.481712085033147</v>
+        <v>-7.469594780210858</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.120094591961184</v>
+        <v>0.1249415138900991</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.334765825361976</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.864713473775778</v>
+        <v>-7.85259616895349</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.03320806485745287</v>
+        <v>-0.02836114292853731</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.334765825361976</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.239698799947055</v>
+        <v>-8.227581495124767</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.1806306793545334</v>
+        <v>-0.1757837574256182</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.709751151533253</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.599229122451057</v>
+        <v>-8.587111817628768</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.3190925050580837</v>
+        <v>-0.3142455831291686</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.709751151533253</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.92562915111607</v>
+        <v>-8.913511846293781</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.4417364965669117</v>
+        <v>-0.4368895746379962</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.036151180198266</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.91915300432251</v>
+        <v>-8.907035699500222</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.4361042872277188</v>
+        <v>-0.4312573652988037</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.029675033404706</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.915462079366099</v>
+        <v>-8.903344774543811</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.4346279172451548</v>
+        <v>-0.4297809953162393</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.029675033404706</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.119720254695963</v>
+        <v>-9.107602949873675</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.5108179902584578</v>
+        <v>-0.5059710683295426</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.157313978018695</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.280359281184328</v>
+        <v>-9.26824197636204</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.5705910463693677</v>
+        <v>-0.5657441244404526</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.272047451021091</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.206889449516879</v>
+        <v>-9.194772144694591</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.5258314122089671</v>
+        <v>-0.5209844902800516</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.198577619353642</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.382013866903423</v>
+        <v>-9.369896562081134</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.5813259584160675</v>
+        <v>-0.5764790364871524</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.373702036740186</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.616465960917912</v>
+        <v>-9.604348656095624</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.6823259609234595</v>
+        <v>-0.677479038994544</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.373702036740186</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.904269805455151</v>
+        <v>-9.892152500632863</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.8041196895123313</v>
+        <v>-0.7992727675834157</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.661505881277424</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.13409425261898</v>
+        <v>-10.12197694779669</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.8949336785393047</v>
+        <v>-0.8900867566103896</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.824153418347585</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.36612317235524</v>
+        <v>-10.35400586753295</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.985051517804695</v>
+        <v>-0.9802045958757799</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.886166115536008</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.31410765838642</v>
+        <v>-10.30199035356414</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.9602549765307691</v>
+        <v>-0.9554080546018531</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.886166115536008</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.45577950011054</v>
+        <v>-10.44366219528826</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.018398940119159</v>
+        <v>-1.013552018190243</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.886166115536008</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.55468624056982</v>
+        <v>-10.54256893574753</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.042908226137996</v>
+        <v>-1.038061304209081</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.985072855995284</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.35553413333272</v>
+        <v>-10.34341682851043</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.9762985168898397</v>
+        <v>-0.9714515949609246</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.81975033004547</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.12968898061331</v>
+        <v>-10.11757167579102</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.8763813827658669</v>
+        <v>-0.8715344608369517</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.777823654458307</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.843414168290614</v>
+        <v>-9.831296863468328</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.7607323132807298</v>
+        <v>-0.7558853913518151</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.777823654458307</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.896309456334901</v>
+        <v>-9.884192151512615</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.7792566543363364</v>
+        <v>-0.7744097324074222</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.772868308369861</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.832240041437185</v>
+        <v>-9.600283420583866</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.7478951841386134</v>
+        <v>-0.655112535797286</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.772868308369861</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.585252791244233</v>
+        <v>-9.353296170390914</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.658837546455298</v>
+        <v>-0.5660548981139706</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.525881058176909</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.321415924040164</v>
+        <v>-9.089459303186844</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.563186280886578</v>
+        <v>-0.4704036325452501</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.525881058176909</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.054174123171766</v>
+        <v>-8.822217502318447</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.4581241210385927</v>
+        <v>-0.3653414726972648</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.525881058176909</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.778364959771281</v>
+        <v>-8.546408338917962</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.3481007706518593</v>
+        <v>-0.2553181223105319</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.436861749898175</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.509297372004301</v>
+        <v>-8.277340751150982</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.239805229399574</v>
+        <v>-0.1470225810582462</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.167794162131196</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.245237433681504</v>
+        <v>-8.013280812828185</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1474415702322074</v>
+        <v>-0.05465892189087951</v>
       </c>
       <c r="F1899" t="n">
         <v>-1.9037342238084</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.538157810176666</v>
+        <v>-7.306201189323347</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.132603245509427</v>
+        <v>0.2253858938507549</v>
       </c>
       <c r="F1900" t="n">
         <v>-1.9037342238084</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.288516780190714</v>
+        <v>-7.056560159337395</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2328032813916492</v>
+        <v>0.3255859297329771</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.654093193822448</v>
@@ -45297,10 +45297,10 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.033974880849639</v>
+        <v>-6.80201825999632</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.3339868623488362</v>
+        <v>0.4267695106901641</v>
       </c>
       <c r="F1902" t="n">
         <v>-1.399551294481372</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.800493658620041</v>
+        <v>-6.568537037766721</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.4353037800785282</v>
+        <v>0.5280864284198556</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.166070072251774</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.620785128476168</v>
+        <v>-6.388828507622849</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.5042949818231177</v>
+        <v>0.5970776301644456</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.108898568089078</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.488509654845282</v>
+        <v>-6.256553033991962</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.5525726580224997</v>
+        <v>0.6453553063638271</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.9766230944581911</v>
@@ -45389,10 +45389,10 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.297909980172129</v>
+        <v>-6.06595335931881</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.6316275885793972</v>
+        <v>0.724410236920725</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.7860234197850382</v>
@@ -45412,10 +45412,10 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.048910181488548</v>
+        <v>-5.816953560635229</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.7441338492764884</v>
+        <v>0.8369164976178163</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.7860234197850382</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.154500171261652</v>
+        <v>-5.922543550408333</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.5739219237680278</v>
+        <v>0.6667045721093556</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.8916134095581425</v>
@@ -45458,10 +45458,10 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.173235073380249</v>
+        <v>-5.94127845252693</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.6149723047976754</v>
+        <v>0.7077549531390033</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.8916134095581425</v>
@@ -45481,10 +45481,10 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-5.896496898709437</v>
+        <v>-5.664540277856117</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.7290465866519953</v>
+        <v>0.8218292349933232</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.7097967484482167</v>
@@ -45504,10 +45504,10 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-5.769604492274366</v>
+        <v>-5.537647871421047</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.7710895629725454</v>
+        <v>0.8638722113138728</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.5829043420131468</v>
@@ -45527,10 +45527,10 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-5.58201698436444</v>
+        <v>-5.350060363511121</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.8391639540414229</v>
+        <v>0.9319466023827503</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.5829043420131468</v>
@@ -45550,10 +45550,10 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-5.339868590910582</v>
+        <v>-5.107911970057263</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.9504856658041092</v>
+        <v>1.043268314145437</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.5829043420131468</v>
@@ -45573,10 +45573,10 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.276639219142234</v>
+        <v>-5.044682598288914</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.9703095349706432</v>
+        <v>1.063092183311971</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.5829043420131468</v>
@@ -45596,10 +45596,10 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.090151526765228</v>
+        <v>-4.858194905911908</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.042402705932023</v>
+        <v>1.13518535427335</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.3964166496361405</v>
@@ -45619,10 +45619,10 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.069002327861784</v>
+        <v>-4.837045707008465</v>
       </c>
       <c r="E1916" t="n">
-        <v>1.058563363730725</v>
+        <v>1.151346012072053</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.3752674507326972</v>
@@ -45642,10 +45642,10 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-4.82523688587834</v>
+        <v>-4.593280265025021</v>
       </c>
       <c r="E1917" t="n">
-        <v>1.151850248871154</v>
+        <v>1.244632897212482</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.3752674507326972</v>
@@ -45665,10 +45665,10 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-4.561208818685079</v>
+        <v>-4.32925219783176</v>
       </c>
       <c r="E1918" t="n">
-        <v>1.259585789668474</v>
+        <v>1.352368438009802</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.1734020519167436</v>
@@ -45688,10 +45688,10 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-4.311358424736005</v>
+        <v>-4.079401803882686</v>
       </c>
       <c r="E1919" t="n">
-        <v>1.352268022231806</v>
+        <v>1.445050670573134</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.1734020519167436</v>
@@ -45711,10 +45711,10 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.007790935732027</v>
+        <v>-3.775834314878707</v>
       </c>
       <c r="E1920" t="n">
-        <v>1.477294141354046</v>
+        <v>1.570076789695374</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.1734020519167436</v>
@@ -45734,10 +45734,10 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-3.934311026880013</v>
+        <v>-3.702354406026693</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.520013610949406</v>
+        <v>1.612796259290733</v>
       </c>
       <c r="F1921" t="n">
         <v>-0.09992214306472924</v>
@@ -45757,10 +45757,10 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-3.70927802721119</v>
+        <v>-3.47732140635787</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.609047288433232</v>
+        <v>1.70182993677456</v>
       </c>
       <c r="F1922" t="n">
         <v>0.1251108566040936</v>
@@ -45780,16 +45780,16 @@
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-3.503730327075221</v>
+        <v>-3.272537160161802</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.695961169541937</v>
+        <v>1.788438436307304</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.3306585567400623</v>
+        <v>0.3298951028001614</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.29620485872981</v>
+        <v>3.295746786365869</v>
       </c>
     </row>
   </sheetData>
